--- a/site/exports/ouc-literature.xlsx
+++ b/site/exports/ouc-literature.xlsx
@@ -1281,7 +1281,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
